--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/BALANCIM VALVULAS.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/BALANCIM VALVULAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,17 +553,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7908073700465</t>
+          <t>7899468026881</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EIXO BALANCIM SMARTFOX CG125 TODAY 1995 A 2004/ TITAN KS/ FAN 2005 A 2008</t>
+          <t>BALANCIM TRILHA BIZ125 2005 A 2010</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -574,20 +574,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7899468026881</t>
+          <t>7908073720906</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BALANCIM TRILHA BIZ125 2005 A 2010</t>
+          <t>BALANCIM SMARTFOX POP110I 2016 A 2021/ BIZ110 2016 A 2021</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -595,12 +599,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7908073720906</t>
+          <t>7908073705320</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BALANCIM SMARTFOX POP110I 2016 A 2021/ BIZ110 2016 A 2021</t>
+          <t>BALANCIM TITAN150 2004 A 2015/ BROS NXR125 2013 A 2015/ NXR150 2014/ FAN 2009</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -608,11 +612,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -620,12 +620,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7908073705320</t>
+          <t>7908073720913</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BALANCIM TITAN150 2004 A 2015/ BROS NXR125 2013 A 2015/ NXR150 2014/ FAN 2009</t>
+          <t>BALANCIM SMARTFOX FAZER250 2006 A 2017/ LANDER XTZ250 2017 A 2019/ TENERE250 2001 A 2019</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -637,41 +637,20 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7908073720913</t>
+          <t> </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BALANCIM SMARTFOX FAZER250 2006 A 2017/ LANDER XTZ250 2017 A 2019/ TENERE250 2001 A 2019</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>26</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/BALANCIM VALVULAS.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/BALANCIM VALVULAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,7 +472,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,7 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,7 +532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,7 +552,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -587,11 +572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -612,7 +592,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -633,24 +612,142 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
